--- a/Web/TestCases/HistorialVentas.xlsx
+++ b/Web/TestCases/HistorialVentas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7231F239-4548-43CE-8F62-0D5A518A4FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCDD58F-DD3F-451C-8723-73C5251E516F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Num</t>
   </si>
@@ -49,59 +49,98 @@
     <t>Sales history page home</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 
+    <t>1. Sales history page home is correctly.</t>
+  </si>
+  <si>
+    <t>Sales' history between dates</t>
+  </si>
+  <si>
+    <t>Filter: Sales' history by pay method</t>
+  </si>
+  <si>
+    <t>Filter: Sales' history by status</t>
+  </si>
+  <si>
+    <t>Filter: Sales' history by waiter</t>
+  </si>
+  <si>
+    <t>Export Sales' history</t>
+  </si>
+  <si>
+    <t>Filter: clean</t>
+  </si>
+  <si>
+    <t>Filter by restaurant</t>
+  </si>
+  <si>
+    <t>SAL001</t>
+  </si>
+  <si>
+    <t>SAL002</t>
+  </si>
+  <si>
+    <t>SAL003</t>
+  </si>
+  <si>
+    <t>SAL004</t>
+  </si>
+  <si>
+    <t>SAL005</t>
+  </si>
+  <si>
+    <t>SAL006</t>
+  </si>
+  <si>
+    <t>SAL007</t>
+  </si>
+  <si>
+    <t>SAL008</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>No se muestra nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects "Historial de Ventas"
 </t>
   </si>
   <si>
-    <t>pte</t>
-  </si>
-  <si>
-    <t>1. Sales history page home is correctly.</t>
-  </si>
-  <si>
-    <t>HISSAL001</t>
-  </si>
-  <si>
-    <t>HISSAL002</t>
-  </si>
-  <si>
-    <t>HISSAL003</t>
-  </si>
-  <si>
-    <t>HISSAL004</t>
-  </si>
-  <si>
-    <t>Sales' history between dates</t>
-  </si>
-  <si>
-    <t>Filter: Sales' history by pay method</t>
-  </si>
-  <si>
-    <t>Filter: Sales' history by status</t>
-  </si>
-  <si>
-    <t>Filter: Sales' history by waiter</t>
-  </si>
-  <si>
-    <t>Export Sales' history</t>
-  </si>
-  <si>
-    <t>Filter: clean</t>
-  </si>
-  <si>
-    <t>Filter by restaurant</t>
-  </si>
-  <si>
-    <t>HISSAL005</t>
-  </si>
-  <si>
-    <t>HISSAL006</t>
-  </si>
-  <si>
-    <t>HISSAL007</t>
-  </si>
-  <si>
-    <t>HISSAL008</t>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects method.</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects waiter.</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects status.</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Limpiar fitros"</t>
+  </si>
+  <si>
+    <t>1. The user selects "desde"
+2. The user selects "hasta"
+3. The user selects restaurant.</t>
+  </si>
+  <si>
+    <t>1. The user selects "Exportar CSV"</t>
+  </si>
+  <si>
+    <t>1. The sales are shown.</t>
+  </si>
+  <si>
+    <t>1. There is not a filter</t>
   </si>
 </sst>
 </file>
@@ -179,7 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -198,9 +237,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -586,92 +622,108 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
-        <v>10</v>
+      <c r="G3" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>10</v>
+      <c r="G4" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>10</v>
+      <c r="G5" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="8" t="s">
-        <v>10</v>
+      <c r="G6" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -680,16 +732,20 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="F7" s="3"/>
-      <c r="G7" s="8" t="s">
-        <v>10</v>
+      <c r="G7" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -698,34 +754,42 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="8" t="s">
-        <v>10</v>
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="8" t="s">
-        <v>10</v>
+      <c r="G9" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="H9" s="4"/>
     </row>
